--- a/Documents/VESIM10_Calibration.xlsx
+++ b/Documents/VESIM10_Calibration.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\TSRP\Gen6-GSE-Elec\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BE873A-058C-40C3-8721-F7E5E0F073E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D056F4-E7DF-42D9-98D3-6B1B9856C0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="3330" windowWidth="29040" windowHeight="15720" xr2:uid="{05A9803B-A475-4F64-B104-4781DCC4642F}"/>
+    <workbookView xWindow="13344" yWindow="0" windowWidth="13632" windowHeight="16176" xr2:uid="{05A9803B-A475-4F64-B104-4781DCC4642F}"/>
   </bookViews>
   <sheets>
     <sheet name="20260221_1" sheetId="1" r:id="rId1"/>
-    <sheet name="テンプレート" sheetId="3" r:id="rId2"/>
+    <sheet name="試験成績表" sheetId="4" r:id="rId2"/>
+    <sheet name="テンプレート" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="15">
   <si>
     <t>試験日</t>
     <rPh sb="0" eb="3">
@@ -105,15 +106,49 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>理論値</t>
+    <rPh sb="0" eb="3">
+      <t>リロンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>圧力媒体</t>
+    <rPh sb="0" eb="4">
+      <t>アツリョクバイタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精製水</t>
+    <rPh sb="0" eb="3">
+      <t>セイセイスイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不明</t>
+    <rPh sb="0" eb="2">
+      <t>フメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CALIB_SLOPE_A</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="185" formatCode="0.0000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="0.0000"/>
+    <numFmt numFmtId="182" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="183" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +180,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Moralerspace Neon JPDOC"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Moralerspace Neon JPDOC"/>
       <family val="3"/>
       <charset val="128"/>
@@ -187,7 +229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -206,10 +248,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="183" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -269,8 +326,12 @@
               <a:t>VESIM10 </a:t>
             </a:r>
             <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>校正</a:t>
+            </a:r>
+            <a:r>
               <a:rPr lang="ja-JP"/>
-              <a:t>公正グラフ</a:t>
+              <a:t>グラフ</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -301,7 +362,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -397,25 +458,25 @@
             <c:numRef>
               <c:f>'20260221_1'!$B$4:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_);[Red]\(0.00\)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4.08</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.25</c:v>
+                  <c:v>6.08</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.42</c:v>
+                  <c:v>7.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.58</c:v>
+                  <c:v>10.199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.739999999999998</c:v>
+                  <c:v>12.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19.91</c:v>
+                  <c:v>14.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -430,19 +491,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1</c:v>
+                  <c:v>1.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.2</c:v>
+                  <c:v>2.2999999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.1999999999999993</c:v>
+                  <c:v>4.74</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.9</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -546,11 +607,11 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00_);[Red]\(0.00\)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -668,7 +729,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -806,8 +867,535 @@
               <a:t>VESIM10 </a:t>
             </a:r>
             <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>校正</a:t>
+            </a:r>
+            <a:r>
               <a:rPr lang="ja-JP"/>
-              <a:t>公正グラフ</a:t>
+              <a:t>グラフ</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>試験成績表!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>マスタ圧力計 [MPa]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                      <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>試験成績表!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3.99</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>試験成績表!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5104-4880-B82A-F364B6ED8D8E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1514230575"/>
+        <c:axId val="1514231055"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1514230575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                    <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>電流</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
+                  <a:t>[mA]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                  <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1514231055"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1514231055"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                    <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>マスタ圧力 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>[MPa]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                  <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1514230575"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+          <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Moralerspace Neon JPDOC" panose="020B0503020203020207" pitchFamily="50" charset="-128"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>VESIM10 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>校正</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP"/>
+              <a:t>グラフ</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -1385,6 +1973,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1902,6 +2530,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2459,6 +3603,49 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>147669</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2497</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>369766</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>124810</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8125F122-D673-4FD9-A23B-8B21F711AAC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2818,7 +4005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB018504-CE38-4303-A560-14B7652FB1C2}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="2"/>
@@ -2834,11 +4021,15 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="11">
+        <v>46074</v>
+      </c>
       <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="O1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2867,85 +4058,100 @@
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="12">
         <v>4.08</v>
       </c>
       <c r="C4" s="4">
         <v>0</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
-        <v>7.25</v>
+      <c r="B5" s="12">
+        <v>6.08</v>
       </c>
       <c r="C5" s="4">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="4">
-        <v>10.42</v>
+      <c r="B6" s="12">
+        <v>7.95</v>
       </c>
       <c r="C6" s="4">
-        <v>4.2</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
-        <v>13.58</v>
+      <c r="B7" s="12">
+        <v>10.199999999999999</v>
       </c>
       <c r="C7" s="4">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="4">
-        <v>16.739999999999998</v>
+      <c r="B8" s="12">
+        <v>12.6</v>
       </c>
       <c r="C8" s="4">
-        <v>8.1999999999999993</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="4">
-        <v>19.91</v>
+      <c r="B9" s="12">
+        <v>14.2</v>
       </c>
       <c r="C9" s="4">
-        <v>9.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6">
         <f>SLOPE(C4:C9,B4:B9)</f>
-        <v>0.62646781455341927</v>
-      </c>
+        <v>0.57765590625809671</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10">
+        <f>10/16</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D22" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{4007C36E-A77C-45ED-B8F2-7CF02FA2172E}">
-      <formula1>$O$1:$O$3</formula1>
+      <formula1>$O$1:$O$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2954,6 +4160,150 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716AA1EB-2423-4E6B-BC1C-43D3323E71B1}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="2"/>
+    <col min="2" max="2" width="14.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" style="2" customWidth="1"/>
+    <col min="5" max="14" width="8.7265625" style="2"/>
+    <col min="15" max="15" width="8.7265625" style="1"/>
+    <col min="16" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11">
+        <v>45309</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="O3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4">
+        <v>3.99</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4">
+        <v>11.97</v>
+      </c>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4">
+        <v>20.02</v>
+      </c>
+      <c r="C6" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <f>SLOPE(C4:C9,B4:B9)</f>
+        <v>0.62382635289502641</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10">
+        <f>10/16</f>
+        <v>0.625</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{9C838551-CD13-41F7-B8C4-2364B50667FA}">
+      <formula1>$O$1:$O$10</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10306D6-57BD-4614-878C-5CDEC0D0A417}">
   <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2968,12 +4318,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="4"/>
       <c r="O1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2984,13 +4336,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3"/>
@@ -2999,68 +4351,71 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>4.08</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>0</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>7.25</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>2.1</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>10.42</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>4.2</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>13.58</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>5.8</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>16.739999999999998</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>8.1999999999999993</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>19.91</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>9.9</v>
       </c>
     </row>
@@ -3068,7 +4423,7 @@
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{CFA3A91B-39FB-4CBE-B656-6F172A3E63A1}">
-      <formula1>$O$1:$O$3</formula1>
+      <formula1>$O$1:$O$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
